--- a/Config/Bullet.xlsx
+++ b/Config/Bullet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F024E36-8E8F-4F6A-8650-6FE07883AEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D31460-517C-4356-9715-EEFED627D6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="3810" windowWidth="21810" windowHeight="23430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5720" yWindow="3280" windowWidth="32720" windowHeight="25860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -670,11 +670,14 @@
       <c r="B6">
         <v>2</v>
       </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="F6">
         <v>1000</v>
